--- a/Result/profitability/3060.xlsx
+++ b/Result/profitability/3060.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.155</v>
+        <v>0.23875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.75625</v>
+        <v>13.38625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30625</v>
+        <v>0.29625</v>
       </c>
       <c r="N3" t="n">
-        <v>12.7625</v>
+        <v>12.58125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.99</v>
       </c>
       <c r="M4" t="n">
-        <v>0.37625</v>
+        <v>0.3925</v>
       </c>
       <c r="N4" t="n">
-        <v>12.0575</v>
+        <v>12.24375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5175000000000001</v>
+        <v>0.6375</v>
       </c>
       <c r="N5" t="n">
-        <v>11.7725</v>
+        <v>12.28625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6812499999999999</v>
+        <v>0.735</v>
       </c>
       <c r="N6" t="n">
-        <v>11.68875</v>
+        <v>12.34875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>-1.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5525</v>
+        <v>0.5874999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>11.8025</v>
+        <v>11.9875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>0.755</v>
+        <v>0.7575</v>
       </c>
       <c r="N8" t="n">
-        <v>12.08625</v>
+        <v>12.06125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1164</v>
+      </c>
+      <c r="D75" t="n">
+        <v>987</v>
+      </c>
+      <c r="E75" t="n">
+        <v>177</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>64</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04874999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.23125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01999999999999996</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.06060606060606055</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2000000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0129870129870131</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.573770491803279</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.109999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3706041478809738</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
